--- a/data/trans_orig/IP07C10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39134</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14551</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21443</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30279</t>
+          <t>30854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44577</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>21220</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42792</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>43066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60489</t>
+          <t>60127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81168</t>
+          <t>82228</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>27913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51126</t>
+          <t>50202</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70141</t>
+          <t>70471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25791</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>41515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30483</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>49317</t>
+          <t>49654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>39170</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55661</t>
+          <t>56230</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>87482</t>
+          <t>87287</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>112697</t>
+          <t>112624</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>100288</t>
+          <t>99578</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>126097</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>194864</t>
+          <t>192972</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>230719</t>
+          <t>231167</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>100386</t>
+          <t>99763</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125746</t>
+          <t>126221</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104011</t>
+          <t>103720</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>131082</t>
+          <t>129961</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>210141</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>247113</t>
+          <t>248055</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>35182</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>55679</t>
+          <t>54183</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>42638</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>64191</t>
+          <t>64628</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>84307</t>
+          <t>82671</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>112052</t>
+          <t>111927</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>34006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>31220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>23378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>28437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>40493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25679</t>
+          <t>25947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28989</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>42385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>33287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48105</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56533</t>
+          <t>57022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76851</t>
+          <t>77443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32485</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47270</t>
+          <t>47459</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88606</t>
+          <t>88973</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31579</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33265</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44680</t>
+          <t>43112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>63530</t>
+          <t>62891</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>28090</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>39033</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77307</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24681</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34967</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20965</t>
+          <t>21191</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>87257</t>
+          <t>87245</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>114284</t>
+          <t>113325</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>98427</t>
+          <t>98303</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>124007</t>
+          <t>124345</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>193448</t>
+          <t>191113</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>229774</t>
+          <t>230871</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>119460</t>
+          <t>119624</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>147355</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>124043</t>
+          <t>123194</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>150474</t>
+          <t>150960</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>251820</t>
+          <t>248103</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>289827</t>
+          <t>290322</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>34091</t>
+          <t>34158</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>53001</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49556</t>
+          <t>49988</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>69186</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>96487</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27467</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27415</t>
+          <t>27526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41520</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21007</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15710</t>
+          <t>15283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>46519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>24916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31108</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47407</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>17875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16789</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>8479</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>40789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56381</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28843</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44364</t>
+          <t>43720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>73398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95753</t>
+          <t>97625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33727</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50357</t>
+          <t>50475</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53342</t>
+          <t>53249</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>75041</t>
+          <t>73855</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98198</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>36832</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>36824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>43828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>62946</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>24135</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>24680</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38218</t>
+          <t>38397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>51994</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71668</t>
+          <t>70946</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>21769</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35607</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>112395</t>
+          <t>114028</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>143101</t>
+          <t>143195</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>119242</t>
+          <t>119959</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>150275</t>
+          <t>152381</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>242907</t>
+          <t>241620</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>283270</t>
+          <t>282570</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>121430</t>
+          <t>120865</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>151911</t>
+          <t>149474</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>127799</t>
+          <t>125965</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>158043</t>
+          <t>156035</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>255830</t>
+          <t>256750</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>298094</t>
+          <t>300478</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>60909</t>
+          <t>60037</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>51907</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>75494</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>104885</t>
+          <t>105240</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
